--- a/tiflow-chargeitem/build/0.9.0/StructureDefinition-GEM-ERPCHRG-PR-ChargeItem.xlsx
+++ b/tiflow-chargeitem/build/0.9.0/StructureDefinition-GEM-ERPCHRG-PR-ChargeItem.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4365" uniqueCount="643">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4346" uniqueCount="626">
   <si>
     <t>Property</t>
   </si>
@@ -496,163 +496,157 @@
     <t>Meta.security</t>
   </si>
   <si>
+    <t>ChargeItem.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>ChargeItem.implicitRules</t>
+  </si>
+  <si>
+    <t>A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+  </si>
+  <si>
+    <t>Resource.implicitRules</t>
+  </si>
+  <si>
+    <t>ChargeItem.language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Language of the resource content</t>
+  </si>
+  <si>
+    <t>The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>A human language.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+  </si>
+  <si>
+    <t>Resource.language</t>
+  </si>
+  <si>
+    <t>ChargeItem.text</t>
+  </si>
+  <si>
+    <t>narrative
+htmlxhtmldisplay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narrative
+</t>
+  </si>
+  <si>
+    <t>Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+  </si>
+  <si>
+    <t>DomainResource.text</t>
+  </si>
+  <si>
+    <t>Act.text?</t>
+  </si>
+  <si>
+    <t>ChargeItem.contained</t>
+  </si>
+  <si>
+    <t>inline resources
+anonymous resourcescontained resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+  </si>
+  <si>
+    <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>ChargeItem.extension</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ChargeItem.extension:markingFlag</t>
+  </si>
+  <si>
+    <t>markingFlag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://gematik.de/fhir/erpchrg/StructureDefinition/GEM_ERPCHRG_EX_MarkingFlag}
+</t>
+  </si>
+  <si>
+    <t>Flag list whether submitted Abrechnungsinformationen for PKV, Taxes, Subsidy</t>
+  </si>
+  <si>
+    <t>Optional Extension for ChargeItem-Ressources in eRx workflow</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
-    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
-    <t>ChargeItem.meta.tag</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
-  </si>
-  <si>
-    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
-  </si>
-  <si>
-    <t>Meta.tag</t>
-  </si>
-  <si>
-    <t>ChargeItem.implicitRules</t>
-  </si>
-  <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
-  </si>
-  <si>
-    <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>ChargeItem.language</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
-  </si>
-  <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>A human language.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
-  </si>
-  <si>
-    <t>Resource.language</t>
-  </si>
-  <si>
-    <t>ChargeItem.text</t>
-  </si>
-  <si>
-    <t>narrative
-htmlxhtmldisplay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative
-</t>
-  </si>
-  <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
-  </si>
-  <si>
-    <t>DomainResource.text</t>
-  </si>
-  <si>
-    <t>Act.text?</t>
-  </si>
-  <si>
-    <t>ChargeItem.contained</t>
-  </si>
-  <si>
-    <t>inline resources
-anonymous resourcescontained resources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
-  </si>
-  <si>
-    <t>DomainResource.contained</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>ChargeItem.extension</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ChargeItem.extension:markingFlag</t>
-  </si>
-  <si>
-    <t>markingFlag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://gematik.de/fhir/erpchrg/StructureDefinition/GEM_ERPCHRG_EX_MarkingFlag}
-</t>
-  </si>
-  <si>
-    <t>Flag list whether submitted Abrechnungsinformationen for PKV, Taxes, Subsidy</t>
-  </si>
-  <si>
-    <t>Optional Extension for ChargeItem-Ressources in eRx workflow</t>
-  </si>
-  <si>
     <t>ChargeItem.modifierExtension</t>
   </si>
   <si>
@@ -871,15 +865,7 @@
     <t>Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
-    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
-Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
-  </si>
-  <si>
     <t>Identifier.period</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
   </si>
   <si>
     <t>CX.7 + CX.8</t>
@@ -910,10 +896,6 @@
     <t>Identifier.assigner</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
   </si>
   <si>
@@ -966,9 +948,6 @@
   </si>
   <si>
     <t>References the (external) source of pricing information, rules of application for the code this ChargeItem uses.</t>
-  </si>
-  <si>
-    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
   </si>
   <si>
     <t>Event.instantiates</t>
@@ -993,9 +972,6 @@
     <t>References the source of pricing information, rules of application for the code this ChargeItem uses.</t>
   </si>
   <si>
-    <t>see [Canonical References](http://hl7.org/fhir/R4/references.html#canonical)</t>
-  </si>
-  <si>
     <t>ChargeItem.status</t>
   </si>
   <si>
@@ -1044,9 +1020,6 @@
     <t>ChargeItems can be grouped to larger ChargeItems covering the whole set.</t>
   </si>
   <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
     <t>E.g. Drug administration as part of a procedure, procedure as part of observation, etc.</t>
   </si>
   <si>
@@ -1069,9 +1042,6 @@
     <t>A code that identifies the charge, like a billing code.</t>
   </si>
   <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
-  </si>
-  <si>
     <t>Example set of codes that can be used for billing purposes.</t>
   </si>
   <si>
@@ -1205,9 +1175,6 @@
   </si>
   <si>
     <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
@@ -1375,9 +1342,6 @@
     <t>Reference.identifier</t>
   </si>
   <si>
-    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
-  </si>
-  <si>
     <t>ChargeItem.subject.display</t>
   </si>
   <si>
@@ -1584,9 +1548,6 @@
     <t>FT1.13</t>
   </si>
   <si>
-    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
-  </si>
-  <si>
     <t>ChargeItem.quantity</t>
   </si>
   <si>
@@ -1603,16 +1564,9 @@
     <t>In many cases this may just be a value, if the underlying units are implicit in the definition of the charge item code.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}</t>
-  </si>
-  <si>
     <t>FT1.10</t>
   </si>
   <si>
-    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
-  </si>
-  <si>
     <t>ChargeItem.bodysite</t>
   </si>
   <si>
@@ -1629,9 +1583,6 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE</t>
   </si>
   <si>
     <t>.targetBodySiteCode</t>
@@ -1675,9 +1626,6 @@
     <t>FT1.22</t>
   </si>
   <si>
-    <t>MO</t>
-  </si>
-  <si>
     <t>ChargeItem.overrideReason</t>
   </si>
   <si>
@@ -1842,9 +1790,6 @@
   </si>
   <si>
     <t>Comments made about the event by the performer, subject or other participants.</t>
-  </si>
-  <si>
-    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
   </si>
   <si>
     <t>Event.note</t>
@@ -2367,7 +2312,7 @@
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="53.91015625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="39.109375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="87.9765625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
@@ -3726,7 +3671,7 @@
         <v>77</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>98</v>
@@ -3735,10 +3680,10 @@
         <v>75</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>156</v>
+        <v>75</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>75</v>
@@ -3746,10 +3691,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3775,13 +3720,13 @@
         <v>146</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3807,31 +3752,31 @@
         <v>75</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -3840,7 +3785,7 @@
         <v>77</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>98</v>
@@ -3849,10 +3794,10 @@
         <v>75</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>156</v>
+        <v>75</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>75</v>
@@ -3860,10 +3805,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3889,13 +3834,13 @@
         <v>128</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3945,7 +3890,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -3974,10 +3919,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4000,16 +3945,16 @@
         <v>75</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4035,31 +3980,31 @@
         <v>75</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="Y15" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -4088,14 +4033,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4114,16 +4059,16 @@
         <v>75</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="L16" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4173,7 +4118,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -4194,7 +4139,7 @@
         <v>75</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>75</v>
@@ -4202,14 +4147,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4228,16 +4173,16 @@
         <v>75</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="N17" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="L17" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4287,7 +4232,7 @@
         <v>75</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -4308,7 +4253,7 @@
         <v>75</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>75</v>
@@ -4316,10 +4261,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4345,10 +4290,10 @@
         <v>107</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4389,9 +4334,7 @@
       <c r="AB18" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="AC18" t="s" s="2">
-        <v>112</v>
-      </c>
+      <c r="AC18" s="2"/>
       <c r="AD18" t="s" s="2">
         <v>75</v>
       </c>
@@ -4399,7 +4342,7 @@
         <v>140</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -4428,13 +4371,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>75</v>
@@ -4456,13 +4399,13 @@
         <v>75</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4513,7 +4456,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -4522,7 +4465,7 @@
         <v>77</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>75</v>
+        <v>201</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>115</v>
@@ -4542,10 +4485,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4571,16 +4514,16 @@
         <v>107</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>110</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>75</v>
@@ -4617,19 +4560,19 @@
         <v>75</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -4650,7 +4593,7 @@
         <v>75</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>75</v>
@@ -4658,10 +4601,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4684,17 +4627,17 @@
         <v>87</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="L21" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>75</v>
@@ -4731,10 +4674,10 @@
         <v>75</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>75</v>
@@ -4743,7 +4686,7 @@
         <v>140</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -4752,33 +4695,33 @@
         <v>77</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AL21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>219</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>75</v>
@@ -4800,17 +4743,17 @@
         <v>87</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>75</v>
@@ -4859,7 +4802,7 @@
         <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -4868,30 +4811,30 @@
         <v>77</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AL22" t="s" s="2">
+      <c r="AN22" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>219</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5000,10 +4943,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5114,10 +5057,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5140,19 +5083,19 @@
         <v>87</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>75</v>
@@ -5177,31 +5120,31 @@
         <v>75</v>
       </c>
       <c r="X25" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="Z25" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="Y25" t="s" s="2">
+      <c r="AA25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -5219,10 +5162,10 @@
         <v>75</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>75</v>
@@ -5230,10 +5173,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5256,19 +5199,19 @@
         <v>87</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>75</v>
@@ -5296,29 +5239,29 @@
         <v>150</v>
       </c>
       <c r="Y26" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="Z26" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>248</v>
-      </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
       </c>
@@ -5326,7 +5269,7 @@
         <v>86</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>98</v>
@@ -5335,10 +5278,10 @@
         <v>75</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>75</v>
@@ -5346,10 +5289,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5375,65 +5318,65 @@
         <v>128</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="S27" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T27" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
@@ -5451,10 +5394,10 @@
         <v>75</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>75</v>
@@ -5462,10 +5405,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5491,13 +5434,13 @@
         <v>100</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5511,7 +5454,7 @@
         <v>75</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>75</v>
@@ -5547,7 +5490,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
@@ -5565,10 +5508,10 @@
         <v>75</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>75</v>
@@ -5576,10 +5519,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5602,17 +5545,15 @@
         <v>87</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="L29" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>275</v>
-      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>75</v>
@@ -5661,7 +5602,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -5670,19 +5611,19 @@
         <v>86</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>277</v>
+        <v>98</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>75</v>
@@ -5690,10 +5631,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5716,16 +5657,16 @@
         <v>87</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5775,7 +5716,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -5784,19 +5725,19 @@
         <v>86</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>287</v>
+        <v>98</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>75</v>
@@ -5804,13 +5745,13 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>75</v>
@@ -5832,17 +5773,17 @@
         <v>87</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>75</v>
@@ -5891,7 +5832,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -5900,30 +5841,30 @@
         <v>77</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AL31" t="s" s="2">
+      <c r="AN31" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>219</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6032,10 +5973,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6146,10 +6087,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6172,19 +6113,19 @@
         <v>87</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="N34" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>75</v>
@@ -6209,31 +6150,31 @@
         <v>75</v>
       </c>
       <c r="X34" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="Z34" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="Y34" t="s" s="2">
+      <c r="AA34" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF34" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -6251,10 +6192,10 @@
         <v>75</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>75</v>
@@ -6262,10 +6203,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6288,19 +6229,19 @@
         <v>87</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>75</v>
@@ -6328,29 +6269,29 @@
         <v>150</v>
       </c>
       <c r="Y35" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF35" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="Z35" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>248</v>
-      </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
       </c>
@@ -6358,7 +6299,7 @@
         <v>86</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>98</v>
@@ -6367,10 +6308,10 @@
         <v>75</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>75</v>
@@ -6378,10 +6319,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6407,29 +6348,29 @@
         <v>128</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="N36" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="U36" t="s" s="2">
         <v>75</v>
@@ -6465,7 +6406,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -6483,10 +6424,10 @@
         <v>75</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>75</v>
@@ -6494,10 +6435,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6523,13 +6464,13 @@
         <v>100</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="N37" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6543,7 +6484,7 @@
         <v>75</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>75</v>
@@ -6579,7 +6520,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -6597,10 +6538,10 @@
         <v>75</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>75</v>
@@ -6608,10 +6549,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6634,17 +6575,15 @@
         <v>87</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="L38" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>275</v>
-      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>75</v>
@@ -6693,7 +6632,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -6702,19 +6641,19 @@
         <v>86</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>277</v>
+        <v>98</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>75</v>
@@ -6722,10 +6661,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6748,16 +6687,16 @@
         <v>87</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6807,7 +6746,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -6816,19 +6755,19 @@
         <v>86</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>287</v>
+        <v>98</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>75</v>
@@ -6836,10 +6775,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6865,14 +6804,12 @@
         <v>128</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>306</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>75</v>
@@ -6921,7 +6858,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -6936,13 +6873,13 @@
         <v>98</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>75</v>
@@ -6950,10 +6887,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6976,17 +6913,15 @@
         <v>75</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>314</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>75</v>
@@ -7035,7 +6970,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -7050,13 +6985,13 @@
         <v>98</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>75</v>
@@ -7064,10 +6999,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7090,16 +7025,16 @@
         <v>87</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7107,7 +7042,7 @@
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="S42" t="s" s="2">
         <v>75</v>
@@ -7125,13 +7060,13 @@
         <v>75</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>75</v>
@@ -7149,7 +7084,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>86</v>
@@ -7164,28 +7099,28 @@
         <v>98</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>324</v>
+        <v>317</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7204,19 +7139,17 @@
         <v>75</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>75</v>
@@ -7265,7 +7198,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -7274,19 +7207,19 @@
         <v>77</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>287</v>
+        <v>98</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>75</v>
@@ -7294,14 +7227,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7320,17 +7253,15 @@
         <v>87</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>338</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>75</v>
@@ -7355,13 +7286,13 @@
         <v>75</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>75</v>
@@ -7379,7 +7310,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>86</v>
@@ -7388,30 +7319,30 @@
         <v>86</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>344</v>
+        <v>335</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7520,10 +7451,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7634,10 +7565,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7663,16 +7594,16 @@
         <v>146</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>75</v>
@@ -7721,7 +7652,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -7730,7 +7661,7 @@
         <v>77</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>98</v>
@@ -7739,10 +7670,10 @@
         <v>75</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>75</v>
@@ -7750,10 +7681,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7862,10 +7793,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7976,10 +7907,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8005,23 +7936,23 @@
         <v>128</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="S50" t="s" s="2">
         <v>75</v>
@@ -8063,7 +7994,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -8081,10 +8012,10 @@
         <v>75</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>75</v>
@@ -8092,10 +8023,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8121,13 +8052,13 @@
         <v>100</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8177,7 +8108,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -8195,10 +8126,10 @@
         <v>75</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>75</v>
@@ -8206,10 +8137,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8232,24 +8163,24 @@
         <v>87</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="S52" t="s" s="2">
         <v>75</v>
@@ -8291,7 +8222,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -8309,10 +8240,10 @@
         <v>75</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>75</v>
@@ -8320,10 +8251,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8349,16 +8280,14 @@
         <v>100</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>384</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>75</v>
@@ -8407,7 +8336,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -8425,10 +8354,10 @@
         <v>75</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>75</v>
@@ -8436,10 +8365,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8462,19 +8391,19 @@
         <v>87</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>75</v>
@@ -8523,7 +8452,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -8541,10 +8470,10 @@
         <v>75</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>75</v>
@@ -8552,10 +8481,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8581,16 +8510,16 @@
         <v>100</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>75</v>
@@ -8639,7 +8568,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -8657,10 +8586,10 @@
         <v>75</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>75</v>
@@ -8668,14 +8597,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8694,19 +8623,17 @@
         <v>87</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>75</v>
@@ -8755,7 +8682,7 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>86</v>
@@ -8764,30 +8691,30 @@
         <v>86</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>287</v>
+        <v>98</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>415</v>
+        <v>405</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8896,10 +8823,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9010,10 +8937,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9039,13 +8966,13 @@
         <v>100</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9095,7 +9022,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -9104,7 +9031,7 @@
         <v>86</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>98</v>
@@ -9116,7 +9043,7 @@
         <v>75</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>75</v>
@@ -9124,10 +9051,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9153,13 +9080,13 @@
         <v>128</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9188,10 +9115,10 @@
         <v>150</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>75</v>
@@ -9209,7 +9136,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -9230,7 +9157,7 @@
         <v>75</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>75</v>
@@ -9238,10 +9165,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9264,16 +9191,16 @@
         <v>87</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9323,7 +9250,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -9332,7 +9259,7 @@
         <v>86</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>98</v>
@@ -9341,10 +9268,10 @@
         <v>75</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>437</v>
+        <v>75</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>75</v>
@@ -9352,10 +9279,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9381,13 +9308,13 @@
         <v>100</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9437,7 +9364,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
@@ -9458,7 +9385,7 @@
         <v>75</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>75</v>
@@ -9466,14 +9393,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9492,19 +9419,17 @@
         <v>87</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>75</v>
@@ -9553,7 +9478,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -9562,34 +9487,34 @@
         <v>86</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>287</v>
+        <v>98</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>452</v>
+        <v>441</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9608,16 +9533,16 @@
         <v>87</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9667,7 +9592,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -9676,30 +9601,30 @@
         <v>86</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>459</v>
+        <v>448</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>461</v>
+        <v>450</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9722,13 +9647,13 @@
         <v>75</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9779,7 +9704,7 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -9788,19 +9713,19 @@
         <v>77</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>466</v>
+        <v>455</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>75</v>
@@ -9808,10 +9733,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9920,10 +9845,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9993,16 +9918,16 @@
         <v>75</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
         <v>114</v>
@@ -10034,14 +9959,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>471</v>
+        <v>460</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>471</v>
+        <v>460</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>472</v>
+        <v>461</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10063,16 +9988,16 @@
         <v>107</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>473</v>
+        <v>462</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>110</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>75</v>
@@ -10121,7 +10046,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>475</v>
+        <v>464</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -10142,7 +10067,7 @@
         <v>75</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>75</v>
@@ -10150,10 +10075,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10176,17 +10101,15 @@
         <v>75</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>338</v>
-      </c>
+        <v>467</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>75</v>
@@ -10211,13 +10134,13 @@
         <v>75</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>75</v>
@@ -10235,7 +10158,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -10244,19 +10167,19 @@
         <v>86</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>481</v>
+        <v>470</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>75</v>
@@ -10264,10 +10187,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10290,17 +10213,15 @@
         <v>75</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>485</v>
+        <v>474</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>475</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>75</v>
@@ -10349,7 +10270,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>86</v>
@@ -10358,30 +10279,30 @@
         <v>86</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>287</v>
+        <v>98</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>487</v>
+        <v>476</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>489</v>
+        <v>478</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>490</v>
+        <v>479</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>490</v>
+        <v>479</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10404,16 +10325,16 @@
         <v>75</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>491</v>
+        <v>480</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>492</v>
+        <v>481</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>493</v>
+        <v>482</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10463,7 +10384,7 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>490</v>
+        <v>479</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -10472,19 +10393,19 @@
         <v>86</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>287</v>
+        <v>98</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>487</v>
+        <v>476</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>494</v>
+        <v>483</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>75</v>
@@ -10492,10 +10413,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>495</v>
+        <v>484</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>495</v>
+        <v>484</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10518,16 +10439,16 @@
         <v>75</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>496</v>
+        <v>485</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>497</v>
+        <v>486</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>498</v>
+        <v>487</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10577,7 +10498,7 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>495</v>
+        <v>484</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
@@ -10586,19 +10507,19 @@
         <v>86</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>287</v>
+        <v>98</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>494</v>
+        <v>483</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>75</v>
@@ -10606,10 +10527,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10632,16 +10553,16 @@
         <v>75</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>500</v>
+        <v>489</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10691,7 +10612,7 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>76</v>
@@ -10700,19 +10621,19 @@
         <v>86</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>287</v>
+        <v>98</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>503</v>
+        <v>492</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>504</v>
+        <v>75</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>75</v>
@@ -10720,10 +10641,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10746,16 +10667,16 @@
         <v>87</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10805,7 +10726,7 @@
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>76</v>
@@ -10814,19 +10735,19 @@
         <v>86</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>510</v>
+        <v>98</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>511</v>
+        <v>498</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>512</v>
+        <v>75</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>75</v>
@@ -10834,10 +10755,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>513</v>
+        <v>499</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>513</v>
+        <v>499</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10860,16 +10781,16 @@
         <v>87</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>514</v>
+        <v>500</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>515</v>
+        <v>501</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>516</v>
+        <v>502</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10895,13 +10816,13 @@
         <v>75</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>517</v>
+        <v>503</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>518</v>
+        <v>504</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>75</v>
@@ -10919,7 +10840,7 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>513</v>
+        <v>499</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
@@ -10928,7 +10849,7 @@
         <v>77</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>98</v>
@@ -10937,10 +10858,10 @@
         <v>75</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>519</v>
+        <v>75</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>520</v>
+        <v>505</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>75</v>
@@ -10948,10 +10869,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>521</v>
+        <v>506</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>521</v>
+        <v>506</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10974,16 +10895,16 @@
         <v>75</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>522</v>
+        <v>507</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>523</v>
+        <v>508</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>524</v>
+        <v>509</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>525</v>
+        <v>510</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11033,7 +10954,7 @@
         <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>521</v>
+        <v>506</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -11051,7 +10972,7 @@
         <v>75</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>526</v>
+        <v>511</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>75</v>
@@ -11062,10 +10983,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>527</v>
+        <v>512</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>527</v>
+        <v>512</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11088,16 +11009,16 @@
         <v>75</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>528</v>
+        <v>513</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>529</v>
+        <v>514</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>530</v>
+        <v>515</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>531</v>
+        <v>516</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11147,7 +11068,7 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>527</v>
+        <v>512</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
@@ -11156,7 +11077,7 @@
         <v>86</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>98</v>
@@ -11165,10 +11086,10 @@
         <v>75</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>532</v>
+        <v>517</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>533</v>
+        <v>75</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>75</v>
@@ -11176,10 +11097,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>534</v>
+        <v>518</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>534</v>
+        <v>518</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11205,13 +11126,13 @@
         <v>100</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>535</v>
+        <v>519</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>536</v>
+        <v>520</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>537</v>
+        <v>521</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11261,7 +11182,7 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>534</v>
+        <v>518</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
@@ -11290,10 +11211,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>538</v>
+        <v>522</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>538</v>
+        <v>522</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11316,16 +11237,16 @@
         <v>87</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>539</v>
+        <v>523</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>540</v>
+        <v>524</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>541</v>
+        <v>525</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>542</v>
+        <v>526</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11375,7 +11296,7 @@
         <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>538</v>
+        <v>522</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
@@ -11384,30 +11305,30 @@
         <v>86</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>287</v>
+        <v>98</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>489</v>
+        <v>478</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>543</v>
+        <v>527</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>543</v>
+        <v>527</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11516,10 +11437,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>544</v>
+        <v>528</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>544</v>
+        <v>528</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11630,10 +11551,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>545</v>
+        <v>529</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>545</v>
+        <v>529</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11659,13 +11580,13 @@
         <v>100</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11715,7 +11636,7 @@
         <v>75</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>76</v>
@@ -11724,7 +11645,7 @@
         <v>86</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>98</v>
@@ -11736,7 +11657,7 @@
         <v>75</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>75</v>
@@ -11744,10 +11665,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>546</v>
+        <v>530</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>546</v>
+        <v>530</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11773,13 +11694,13 @@
         <v>128</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -11808,10 +11729,10 @@
         <v>150</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>75</v>
@@ -11829,7 +11750,7 @@
         <v>75</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>76</v>
@@ -11850,7 +11771,7 @@
         <v>75</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>75</v>
@@ -11858,10 +11779,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>547</v>
+        <v>531</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>547</v>
+        <v>531</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11884,16 +11805,16 @@
         <v>87</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>548</v>
+        <v>532</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -11943,7 +11864,7 @@
         <v>75</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>76</v>
@@ -11952,7 +11873,7 @@
         <v>86</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>98</v>
@@ -11961,10 +11882,10 @@
         <v>75</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>437</v>
+        <v>75</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>75</v>
@@ -11972,10 +11893,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>549</v>
+        <v>533</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>549</v>
+        <v>533</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12001,13 +11922,13 @@
         <v>100</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12057,7 +11978,7 @@
         <v>75</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>76</v>
@@ -12078,7 +11999,7 @@
         <v>75</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>75</v>
@@ -12086,10 +12007,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>550</v>
+        <v>534</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>550</v>
+        <v>534</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12112,16 +12033,16 @@
         <v>87</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>551</v>
+        <v>535</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>552</v>
+        <v>536</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>553</v>
+        <v>537</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>554</v>
+        <v>538</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12171,7 +12092,7 @@
         <v>75</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>550</v>
+        <v>534</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>76</v>
@@ -12200,10 +12121,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>555</v>
+        <v>539</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>555</v>
+        <v>539</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12226,16 +12147,16 @@
         <v>75</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>556</v>
+        <v>540</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>557</v>
+        <v>541</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>558</v>
+        <v>542</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12261,13 +12182,13 @@
         <v>75</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>559</v>
+        <v>543</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>560</v>
+        <v>544</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>75</v>
@@ -12285,7 +12206,7 @@
         <v>75</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>555</v>
+        <v>539</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>76</v>
@@ -12294,30 +12215,30 @@
         <v>77</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>561</v>
+        <v>545</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>562</v>
+        <v>546</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>563</v>
+        <v>547</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>564</v>
+        <v>548</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>565</v>
+        <v>549</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>565</v>
+        <v>549</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12340,17 +12261,15 @@
         <v>75</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>566</v>
+        <v>550</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>567</v>
+        <v>551</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>552</v>
+      </c>
+      <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>75</v>
@@ -12399,7 +12318,7 @@
         <v>75</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>565</v>
+        <v>549</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>76</v>
@@ -12408,30 +12327,30 @@
         <v>77</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>287</v>
+        <v>98</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>569</v>
+        <v>553</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>562</v>
+        <v>546</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>570</v>
+        <v>554</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>564</v>
+        <v>548</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>571</v>
+        <v>555</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>571</v>
+        <v>555</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12454,13 +12373,13 @@
         <v>75</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>572</v>
+        <v>556</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>573</v>
+        <v>557</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>574</v>
+        <v>558</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12487,13 +12406,13 @@
         <v>75</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>575</v>
+        <v>559</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>576</v>
+        <v>560</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>75</v>
@@ -12511,7 +12430,7 @@
         <v>75</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>571</v>
+        <v>555</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>76</v>
@@ -12520,7 +12439,7 @@
         <v>86</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>98</v>
@@ -12532,7 +12451,7 @@
         <v>75</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>577</v>
+        <v>561</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>75</v>
@@ -12540,10 +12459,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>578</v>
+        <v>562</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>578</v>
+        <v>562</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12566,16 +12485,16 @@
         <v>87</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>579</v>
+        <v>563</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>580</v>
+        <v>564</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>581</v>
+        <v>565</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>582</v>
+        <v>566</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12625,7 +12544,7 @@
         <v>75</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>578</v>
+        <v>562</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>76</v>
@@ -12634,10 +12553,10 @@
         <v>77</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>287</v>
+        <v>98</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>75</v>
@@ -12646,7 +12565,7 @@
         <v>75</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>504</v>
+        <v>75</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>75</v>
@@ -12654,10 +12573,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>583</v>
+        <v>567</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>583</v>
+        <v>567</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12680,17 +12599,15 @@
         <v>75</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>584</v>
+        <v>568</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>585</v>
+        <v>569</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>587</v>
-      </c>
+        <v>570</v>
+      </c>
+      <c r="N91" s="2"/>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>75</v>
@@ -12739,7 +12656,7 @@
         <v>75</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>583</v>
+        <v>567</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>76</v>
@@ -12748,19 +12665,19 @@
         <v>77</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>588</v>
+        <v>571</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>589</v>
+        <v>572</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>590</v>
+        <v>573</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>75</v>
@@ -12768,10 +12685,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>591</v>
+        <v>574</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>591</v>
+        <v>574</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12782,7 +12699,7 @@
         <v>76</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>592</v>
+        <v>575</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>87</v>
@@ -12794,17 +12711,15 @@
         <v>75</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>593</v>
+        <v>576</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>594</v>
+        <v>577</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>578</v>
+      </c>
+      <c r="N92" s="2"/>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>75</v>
@@ -12841,7 +12756,7 @@
         <v>75</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>596</v>
+        <v>579</v>
       </c>
       <c r="AC92" s="2"/>
       <c r="AD92" t="s" s="2">
@@ -12851,7 +12766,7 @@
         <v>140</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>591</v>
+        <v>574</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>76</v>
@@ -12860,19 +12775,19 @@
         <v>77</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>287</v>
+        <v>98</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>597</v>
+        <v>580</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>504</v>
+        <v>75</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>75</v>
@@ -12880,13 +12795,13 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>598</v>
+        <v>581</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>591</v>
+        <v>574</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>599</v>
+        <v>582</v>
       </c>
       <c r="D93" t="s" s="2">
         <v>75</v>
@@ -12908,17 +12823,15 @@
         <v>75</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>600</v>
+        <v>583</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>594</v>
+        <v>577</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="N93" s="2"/>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>75</v>
@@ -12967,7 +12880,7 @@
         <v>75</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>591</v>
+        <v>574</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>76</v>
@@ -12976,19 +12889,19 @@
         <v>77</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>287</v>
+        <v>98</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>597</v>
+        <v>580</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>504</v>
+        <v>75</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>75</v>
@@ -12996,10 +12909,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>602</v>
+        <v>585</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13108,10 +13021,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>604</v>
+        <v>587</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>605</v>
+        <v>588</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13222,10 +13135,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>606</v>
+        <v>589</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>607</v>
+        <v>590</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13251,13 +13164,13 @@
         <v>100</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13307,7 +13220,7 @@
         <v>75</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>76</v>
@@ -13316,7 +13229,7 @@
         <v>86</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>98</v>
@@ -13328,7 +13241,7 @@
         <v>75</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>75</v>
@@ -13336,10 +13249,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>608</v>
+        <v>591</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>609</v>
+        <v>592</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13365,13 +13278,13 @@
         <v>128</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13400,10 +13313,10 @@
         <v>150</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>75</v>
@@ -13421,7 +13334,7 @@
         <v>75</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>76</v>
@@ -13442,7 +13355,7 @@
         <v>75</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>75</v>
@@ -13450,10 +13363,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>610</v>
+        <v>593</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>611</v>
+        <v>594</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13476,16 +13389,16 @@
         <v>87</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -13535,7 +13448,7 @@
         <v>75</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>76</v>
@@ -13544,7 +13457,7 @@
         <v>86</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>98</v>
@@ -13553,10 +13466,10 @@
         <v>75</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>437</v>
+        <v>75</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>75</v>
@@ -13564,10 +13477,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>612</v>
+        <v>595</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>613</v>
+        <v>596</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13593,13 +13506,13 @@
         <v>100</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13607,7 +13520,7 @@
       </c>
       <c r="Q99" s="2"/>
       <c r="R99" t="s" s="2">
-        <v>614</v>
+        <v>597</v>
       </c>
       <c r="S99" t="s" s="2">
         <v>75</v>
@@ -13649,7 +13562,7 @@
         <v>75</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>76</v>
@@ -13670,7 +13583,7 @@
         <v>75</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>75</v>
@@ -13678,13 +13591,13 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>615</v>
+        <v>598</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>591</v>
+        <v>574</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>616</v>
+        <v>599</v>
       </c>
       <c r="D100" t="s" s="2">
         <v>75</v>
@@ -13706,17 +13619,15 @@
         <v>75</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>617</v>
+        <v>600</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>594</v>
+        <v>577</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="N100" s="2"/>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>75</v>
@@ -13765,7 +13676,7 @@
         <v>75</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>591</v>
+        <v>574</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>76</v>
@@ -13774,19 +13685,19 @@
         <v>77</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>287</v>
+        <v>98</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>597</v>
+        <v>580</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>504</v>
+        <v>75</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>75</v>
@@ -13794,10 +13705,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>618</v>
+        <v>601</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13906,10 +13817,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>619</v>
+        <v>602</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>605</v>
+        <v>588</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14020,10 +13931,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>620</v>
+        <v>603</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>607</v>
+        <v>590</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14049,13 +13960,13 @@
         <v>100</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -14105,7 +14016,7 @@
         <v>75</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>76</v>
@@ -14114,7 +14025,7 @@
         <v>86</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>98</v>
@@ -14126,7 +14037,7 @@
         <v>75</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>75</v>
@@ -14134,10 +14045,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>621</v>
+        <v>604</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>609</v>
+        <v>592</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14163,13 +14074,13 @@
         <v>128</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -14198,10 +14109,10 @@
         <v>150</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>75</v>
@@ -14219,7 +14130,7 @@
         <v>75</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>76</v>
@@ -14240,7 +14151,7 @@
         <v>75</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>75</v>
@@ -14248,10 +14159,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>622</v>
+        <v>605</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>611</v>
+        <v>594</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14274,16 +14185,16 @@
         <v>87</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14333,7 +14244,7 @@
         <v>75</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>76</v>
@@ -14342,7 +14253,7 @@
         <v>86</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>98</v>
@@ -14351,10 +14262,10 @@
         <v>75</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>437</v>
+        <v>75</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>75</v>
@@ -14362,10 +14273,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>623</v>
+        <v>606</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>613</v>
+        <v>596</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14391,13 +14302,13 @@
         <v>100</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -14405,7 +14316,7 @@
       </c>
       <c r="Q106" s="2"/>
       <c r="R106" t="s" s="2">
-        <v>624</v>
+        <v>607</v>
       </c>
       <c r="S106" t="s" s="2">
         <v>75</v>
@@ -14447,7 +14358,7 @@
         <v>75</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>76</v>
@@ -14468,7 +14379,7 @@
         <v>75</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>75</v>
@@ -14476,13 +14387,13 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>625</v>
+        <v>608</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>591</v>
+        <v>574</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>626</v>
+        <v>609</v>
       </c>
       <c r="D107" t="s" s="2">
         <v>75</v>
@@ -14504,17 +14415,15 @@
         <v>75</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>600</v>
+        <v>583</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>594</v>
+        <v>577</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="N107" s="2"/>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>75</v>
@@ -14563,7 +14472,7 @@
         <v>75</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>591</v>
+        <v>574</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>76</v>
@@ -14572,19 +14481,19 @@
         <v>77</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>287</v>
+        <v>98</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>597</v>
+        <v>580</v>
       </c>
       <c r="AL107" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>504</v>
+        <v>75</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>75</v>
@@ -14592,10 +14501,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>627</v>
+        <v>610</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14704,10 +14613,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>628</v>
+        <v>611</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>605</v>
+        <v>588</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14818,10 +14727,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>629</v>
+        <v>612</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>607</v>
+        <v>590</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14847,13 +14756,13 @@
         <v>100</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -14903,7 +14812,7 @@
         <v>75</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>76</v>
@@ -14912,7 +14821,7 @@
         <v>86</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="AJ110" t="s" s="2">
         <v>98</v>
@@ -14924,7 +14833,7 @@
         <v>75</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>75</v>
@@ -14932,10 +14841,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>630</v>
+        <v>613</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>609</v>
+        <v>592</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14961,13 +14870,13 @@
         <v>128</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -14996,10 +14905,10 @@
         <v>150</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>75</v>
@@ -15017,7 +14926,7 @@
         <v>75</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>76</v>
@@ -15038,7 +14947,7 @@
         <v>75</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>75</v>
@@ -15046,10 +14955,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>631</v>
+        <v>614</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>611</v>
+        <v>594</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15072,16 +14981,16 @@
         <v>87</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -15131,7 +15040,7 @@
         <v>75</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>76</v>
@@ -15140,7 +15049,7 @@
         <v>86</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ112" t="s" s="2">
         <v>98</v>
@@ -15149,10 +15058,10 @@
         <v>75</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>437</v>
+        <v>75</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>75</v>
@@ -15160,10 +15069,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>632</v>
+        <v>615</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>613</v>
+        <v>596</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15189,13 +15098,13 @@
         <v>100</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -15203,7 +15112,7 @@
       </c>
       <c r="Q113" s="2"/>
       <c r="R113" t="s" s="2">
-        <v>633</v>
+        <v>616</v>
       </c>
       <c r="S113" t="s" s="2">
         <v>75</v>
@@ -15245,7 +15154,7 @@
         <v>75</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>76</v>
@@ -15266,7 +15175,7 @@
         <v>75</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>75</v>
@@ -15274,13 +15183,13 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>634</v>
+        <v>617</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>591</v>
+        <v>574</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>635</v>
+        <v>618</v>
       </c>
       <c r="D114" t="s" s="2">
         <v>75</v>
@@ -15302,17 +15211,15 @@
         <v>75</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>600</v>
+        <v>583</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>594</v>
+        <v>577</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="N114" s="2"/>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>75</v>
@@ -15361,7 +15268,7 @@
         <v>75</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>591</v>
+        <v>574</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>76</v>
@@ -15370,19 +15277,19 @@
         <v>77</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>287</v>
+        <v>98</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>597</v>
+        <v>580</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>504</v>
+        <v>75</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>75</v>
@@ -15390,10 +15297,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>636</v>
+        <v>619</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15502,10 +15409,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>637</v>
+        <v>620</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>605</v>
+        <v>588</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15616,10 +15523,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>638</v>
+        <v>621</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>607</v>
+        <v>590</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15645,13 +15552,13 @@
         <v>100</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -15701,7 +15608,7 @@
         <v>75</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>76</v>
@@ -15710,7 +15617,7 @@
         <v>86</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="AJ117" t="s" s="2">
         <v>98</v>
@@ -15722,7 +15629,7 @@
         <v>75</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>75</v>
@@ -15730,10 +15637,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>639</v>
+        <v>622</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>609</v>
+        <v>592</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15759,13 +15666,13 @@
         <v>128</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -15794,10 +15701,10 @@
         <v>150</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>75</v>
@@ -15815,7 +15722,7 @@
         <v>75</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>76</v>
@@ -15836,7 +15743,7 @@
         <v>75</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>75</v>
@@ -15844,10 +15751,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>640</v>
+        <v>623</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>611</v>
+        <v>594</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15870,16 +15777,16 @@
         <v>87</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -15929,7 +15836,7 @@
         <v>75</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>76</v>
@@ -15938,7 +15845,7 @@
         <v>86</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AJ119" t="s" s="2">
         <v>98</v>
@@ -15947,10 +15854,10 @@
         <v>75</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>437</v>
+        <v>75</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>75</v>
@@ -15958,10 +15865,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>641</v>
+        <v>624</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>613</v>
+        <v>596</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15987,13 +15894,13 @@
         <v>100</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -16001,7 +15908,7 @@
       </c>
       <c r="Q120" s="2"/>
       <c r="R120" t="s" s="2">
-        <v>642</v>
+        <v>625</v>
       </c>
       <c r="S120" t="s" s="2">
         <v>75</v>
@@ -16043,7 +15950,7 @@
         <v>75</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>76</v>
@@ -16064,7 +15971,7 @@
         <v>75</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>75</v>
